--- a/src/test/resources/input.xlsx
+++ b/src/test/resources/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amank\Downloads\MakeMyTrip\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA199A8B-707C-4564-ADDA-6D551DC800BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0403EE75-03BD-4363-88BE-257376352B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>New Delhi</t>
+  </si>
+  <si>
+    <t>TC05_Verify_Flight_Booking</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
   </si>
 </sst>
 </file>
@@ -404,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
@@ -491,6 +497,17 @@
       </c>
       <c r="E7" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
